--- a/companies.xlsx
+++ b/companies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GenAI Projects\qr-code-generator-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF7E21C-0476-4F7E-B3E3-DEA4365788E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43ABE47C-59B9-4532-A69E-D3131FBF1B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8BF9E950-9155-4008-9F92-CD3259CD626A}"/>
   </bookViews>
@@ -42,15 +42,9 @@
     <t>https://airobohub.com</t>
   </si>
   <si>
-    <t>https://futuretechsolution.in</t>
-  </si>
-  <si>
     <t>https://microsoft.com</t>
   </si>
   <si>
-    <t>https://openai.com</t>
-  </si>
-  <si>
     <t>https://aistudio.google.com</t>
   </si>
   <si>
@@ -61,16 +55,30 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>www:futuretechsolution.in</t>
+  </si>
+  <si>
+    <t>openai.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -93,14 +101,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -421,10 +432,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -432,42 +443,45 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
+      <c r="A5" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" r:id="rId1" display="www.openai.com" xr:uid="{C6C4DB75-D0FB-4076-9820-2AC63103322C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>